--- a/data/transitionTable.xlsx
+++ b/data/transitionTable.xlsx
@@ -111,7 +111,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -123,12 +123,6 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -181,15 +175,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" quotePrefix="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
@@ -503,37 +494,37 @@
   <dimension ref="A1:AE64"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="5" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="5" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="5" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="5" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="5" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="5" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="5" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="5" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="5" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="5" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="11" max="11" style="5" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="12" max="12" style="5" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="13" max="13" style="5" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="14" max="14" style="5" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="15" max="15" style="5" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="16" max="16" style="5" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="17" max="17" style="5" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="18" max="18" style="5" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="19" max="19" style="5" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="20" max="20" style="5" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="21" max="21" style="5" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="22" max="22" style="5" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="23" max="23" style="5" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="24" max="24" style="5" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="25" max="25" style="5" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="26" max="26" style="5" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="27" max="27" style="5" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="28" max="28" style="5" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="29" max="29" style="5" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="30" max="30" style="5" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="31" max="31" style="5" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="4" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="4" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="4" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="4" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="4" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="4" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="4" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="4" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="4" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="10" max="10" style="4" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="11" max="11" style="4" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="12" max="12" style="4" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="13" max="13" style="4" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="14" max="14" style="4" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="15" max="15" style="4" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="16" max="16" style="4" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="17" max="17" style="4" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="18" max="18" style="4" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="19" max="19" style="4" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="20" max="20" style="4" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="21" max="21" style="4" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="22" max="22" style="4" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="23" max="23" style="4" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="24" max="24" style="4" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="25" max="25" style="4" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="26" max="26" style="4" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="27" max="27" style="4" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="28" max="28" style="4" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="29" max="29" style="4" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="30" max="30" style="4" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="31" max="31" style="4" width="12.43357142857143" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="20.25">
@@ -953,7 +944,7 @@
       <c r="L5" s="3">
         <v>65</v>
       </c>
-      <c r="M5" s="4"/>
+      <c r="M5" s="3"/>
       <c r="N5" s="3">
         <v>65</v>
       </c>
@@ -1046,7 +1037,7 @@
       <c r="L6" s="3">
         <v>65</v>
       </c>
-      <c r="M6" s="4"/>
+      <c r="M6" s="3"/>
       <c r="N6" s="3">
         <v>65</v>
       </c>
@@ -1139,7 +1130,7 @@
       <c r="L7" s="3">
         <v>65</v>
       </c>
-      <c r="M7" s="4"/>
+      <c r="M7" s="3"/>
       <c r="N7" s="3">
         <v>65</v>
       </c>
@@ -1232,7 +1223,7 @@
       <c r="L8" s="3">
         <v>65</v>
       </c>
-      <c r="M8" s="4"/>
+      <c r="M8" s="3"/>
       <c r="N8" s="3">
         <v>65</v>
       </c>
@@ -1420,7 +1411,7 @@
       <c r="L10" s="3">
         <v>65</v>
       </c>
-      <c r="M10" s="4"/>
+      <c r="M10" s="3"/>
       <c r="N10" s="3">
         <v>65</v>
       </c>
@@ -1798,7 +1789,7 @@
       <c r="L14" s="3">
         <v>65</v>
       </c>
-      <c r="M14" s="4"/>
+      <c r="M14" s="3"/>
       <c r="N14" s="3">
         <v>65</v>
       </c>
@@ -1891,7 +1882,7 @@
       <c r="L15" s="3">
         <v>65</v>
       </c>
-      <c r="M15" s="4"/>
+      <c r="M15" s="3"/>
       <c r="N15" s="3">
         <v>65</v>
       </c>
@@ -1984,7 +1975,7 @@
       <c r="L16" s="3">
         <v>65</v>
       </c>
-      <c r="M16" s="4"/>
+      <c r="M16" s="3"/>
       <c r="N16" s="3">
         <v>65</v>
       </c>
@@ -2077,7 +2068,7 @@
       <c r="L17" s="3">
         <v>65</v>
       </c>
-      <c r="M17" s="4"/>
+      <c r="M17" s="3"/>
       <c r="N17" s="3">
         <v>65</v>
       </c>
@@ -2170,7 +2161,7 @@
       <c r="L18" s="3">
         <v>65</v>
       </c>
-      <c r="M18" s="4"/>
+      <c r="M18" s="3"/>
       <c r="N18" s="3">
         <v>65</v>
       </c>
@@ -2263,7 +2254,7 @@
       <c r="L19" s="3">
         <v>65</v>
       </c>
-      <c r="M19" s="4"/>
+      <c r="M19" s="3"/>
       <c r="N19" s="3">
         <v>65</v>
       </c>
@@ -2356,7 +2347,7 @@
       <c r="L20" s="3">
         <v>65</v>
       </c>
-      <c r="M20" s="4"/>
+      <c r="M20" s="3"/>
       <c r="N20" s="3">
         <v>65</v>
       </c>
@@ -2449,7 +2440,7 @@
       <c r="L21" s="3">
         <v>65</v>
       </c>
-      <c r="M21" s="4"/>
+      <c r="M21" s="3"/>
       <c r="N21" s="3">
         <v>65</v>
       </c>
@@ -2542,7 +2533,7 @@
       <c r="L22" s="3">
         <v>65</v>
       </c>
-      <c r="M22" s="4"/>
+      <c r="M22" s="3"/>
       <c r="N22" s="3">
         <v>65</v>
       </c>
@@ -2635,7 +2626,7 @@
       <c r="L23" s="3">
         <v>65</v>
       </c>
-      <c r="M23" s="4"/>
+      <c r="M23" s="3"/>
       <c r="N23" s="3">
         <v>65</v>
       </c>
@@ -2728,7 +2719,7 @@
       <c r="L24" s="3">
         <v>65</v>
       </c>
-      <c r="M24" s="4"/>
+      <c r="M24" s="3"/>
       <c r="N24" s="3">
         <v>65</v>
       </c>
@@ -2821,7 +2812,7 @@
       <c r="L25" s="3">
         <v>65</v>
       </c>
-      <c r="M25" s="4"/>
+      <c r="M25" s="3"/>
       <c r="N25" s="3">
         <v>65</v>
       </c>
@@ -2914,7 +2905,7 @@
       <c r="L26" s="3">
         <v>65</v>
       </c>
-      <c r="M26" s="4"/>
+      <c r="M26" s="3"/>
       <c r="N26" s="3">
         <v>65</v>
       </c>
@@ -3007,7 +2998,7 @@
       <c r="L27" s="3">
         <v>65</v>
       </c>
-      <c r="M27" s="4"/>
+      <c r="M27" s="3"/>
       <c r="N27" s="3">
         <v>65</v>
       </c>
@@ -3195,7 +3186,7 @@
       <c r="L29" s="3">
         <v>65</v>
       </c>
-      <c r="M29" s="4"/>
+      <c r="M29" s="3"/>
       <c r="N29" s="3">
         <v>65</v>
       </c>
@@ -3383,7 +3374,7 @@
       <c r="L31" s="3">
         <v>65</v>
       </c>
-      <c r="M31" s="4"/>
+      <c r="M31" s="3"/>
       <c r="N31" s="3">
         <v>65</v>
       </c>
@@ -3571,7 +3562,7 @@
       <c r="L33" s="3">
         <v>65</v>
       </c>
-      <c r="M33" s="4"/>
+      <c r="M33" s="3"/>
       <c r="N33" s="3">
         <v>65</v>
       </c>
@@ -3664,7 +3655,7 @@
       <c r="L34" s="3">
         <v>65</v>
       </c>
-      <c r="M34" s="4"/>
+      <c r="M34" s="3"/>
       <c r="N34" s="3">
         <v>65</v>
       </c>
@@ -3757,7 +3748,7 @@
       <c r="L35" s="3">
         <v>65</v>
       </c>
-      <c r="M35" s="4"/>
+      <c r="M35" s="3"/>
       <c r="N35" s="3">
         <v>65</v>
       </c>
@@ -3850,7 +3841,7 @@
       <c r="L36" s="3">
         <v>65</v>
       </c>
-      <c r="M36" s="4"/>
+      <c r="M36" s="3"/>
       <c r="N36" s="3">
         <v>65</v>
       </c>
@@ -3943,7 +3934,7 @@
       <c r="L37" s="3">
         <v>65</v>
       </c>
-      <c r="M37" s="4"/>
+      <c r="M37" s="3"/>
       <c r="N37" s="3">
         <v>65</v>
       </c>
@@ -4036,7 +4027,7 @@
       <c r="L38" s="3">
         <v>65</v>
       </c>
-      <c r="M38" s="4"/>
+      <c r="M38" s="3"/>
       <c r="N38" s="3">
         <v>65</v>
       </c>
@@ -4129,7 +4120,7 @@
       <c r="L39" s="3">
         <v>65</v>
       </c>
-      <c r="M39" s="4"/>
+      <c r="M39" s="3"/>
       <c r="N39" s="3">
         <v>65</v>
       </c>
@@ -4222,7 +4213,7 @@
       <c r="L40" s="3">
         <v>65</v>
       </c>
-      <c r="M40" s="4"/>
+      <c r="M40" s="3"/>
       <c r="N40" s="3">
         <v>65</v>
       </c>
@@ -4410,7 +4401,7 @@
       <c r="L42" s="3">
         <v>65</v>
       </c>
-      <c r="M42" s="4"/>
+      <c r="M42" s="3"/>
       <c r="N42" s="3">
         <v>65</v>
       </c>
@@ -4503,7 +4494,7 @@
       <c r="L43" s="3">
         <v>65</v>
       </c>
-      <c r="M43" s="4"/>
+      <c r="M43" s="3"/>
       <c r="N43" s="3">
         <v>65</v>
       </c>
@@ -4596,7 +4587,7 @@
       <c r="L44" s="3">
         <v>65</v>
       </c>
-      <c r="M44" s="4"/>
+      <c r="M44" s="3"/>
       <c r="N44" s="3">
         <v>65</v>
       </c>
@@ -4689,7 +4680,7 @@
       <c r="L45" s="3">
         <v>65</v>
       </c>
-      <c r="M45" s="4"/>
+      <c r="M45" s="3"/>
       <c r="N45" s="3">
         <v>65</v>
       </c>
@@ -4972,7 +4963,7 @@
       <c r="L48" s="3">
         <v>65</v>
       </c>
-      <c r="M48" s="4"/>
+      <c r="M48" s="3"/>
       <c r="N48" s="3">
         <v>65</v>
       </c>
@@ -5065,7 +5056,7 @@
       <c r="L49" s="3">
         <v>65</v>
       </c>
-      <c r="M49" s="4"/>
+      <c r="M49" s="3"/>
       <c r="N49" s="3">
         <v>65</v>
       </c>
@@ -5253,7 +5244,7 @@
       <c r="L51" s="3">
         <v>65</v>
       </c>
-      <c r="M51" s="4"/>
+      <c r="M51" s="3"/>
       <c r="N51" s="3">
         <v>65</v>
       </c>
@@ -5441,7 +5432,7 @@
       <c r="L53" s="3">
         <v>65</v>
       </c>
-      <c r="M53" s="4"/>
+      <c r="M53" s="3"/>
       <c r="N53" s="3">
         <v>65</v>
       </c>
@@ -5534,7 +5525,7 @@
       <c r="L54" s="3">
         <v>65</v>
       </c>
-      <c r="M54" s="4"/>
+      <c r="M54" s="3"/>
       <c r="N54" s="3">
         <v>65</v>
       </c>
@@ -5722,7 +5713,7 @@
       <c r="L56" s="3">
         <v>65</v>
       </c>
-      <c r="M56" s="4"/>
+      <c r="M56" s="3"/>
       <c r="N56" s="3">
         <v>65</v>
       </c>
@@ -5815,7 +5806,7 @@
       <c r="L57" s="3">
         <v>65</v>
       </c>
-      <c r="M57" s="4"/>
+      <c r="M57" s="3"/>
       <c r="N57" s="3">
         <v>65</v>
       </c>
@@ -5908,7 +5899,7 @@
       <c r="L58" s="3">
         <v>65</v>
       </c>
-      <c r="M58" s="4"/>
+      <c r="M58" s="3"/>
       <c r="N58" s="3">
         <v>65</v>
       </c>
@@ -6001,7 +5992,7 @@
       <c r="L59" s="3">
         <v>65</v>
       </c>
-      <c r="M59" s="4"/>
+      <c r="M59" s="3"/>
       <c r="N59" s="3">
         <v>65</v>
       </c>
@@ -6094,7 +6085,7 @@
       <c r="L60" s="3">
         <v>65</v>
       </c>
-      <c r="M60" s="4"/>
+      <c r="M60" s="3"/>
       <c r="N60" s="3">
         <v>65</v>
       </c>
@@ -6187,7 +6178,7 @@
       <c r="L61" s="3">
         <v>65</v>
       </c>
-      <c r="M61" s="4"/>
+      <c r="M61" s="3"/>
       <c r="N61" s="3">
         <v>65</v>
       </c>
@@ -6375,7 +6366,7 @@
       <c r="L63" s="3">
         <v>65</v>
       </c>
-      <c r="M63" s="4"/>
+      <c r="M63" s="3"/>
       <c r="N63" s="3">
         <v>65</v>
       </c>
